--- a/public/archivos/Plantilla mejorada.xlsx
+++ b/public/archivos/Plantilla mejorada.xlsx
@@ -5,30 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08183C01-169D-42DE-90D7-C4247B3D0B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7F8CF8-8D32-47CC-85EE-ECC4354CEC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
-  <si>
-    <t>ESTADO ALUMNO:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t xml:space="preserve">TIPO ID: </t>
   </si>
@@ -36,24 +36,12 @@
     <t>NUMERO:</t>
   </si>
   <si>
-    <t>DEPARTAMENTO DE EXPEDICION:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUNICIPIO DE EXPEDICION: </t>
-  </si>
-  <si>
     <t>GENERO:</t>
   </si>
   <si>
     <t xml:space="preserve">FECHA DE NACIMIENTO: </t>
   </si>
   <si>
-    <t xml:space="preserve">DEPARTAMENTO DE NACIMIENTO: </t>
-  </si>
-  <si>
-    <t>MUNICPIO DE NACIMIENTO:</t>
-  </si>
-  <si>
     <t>PRIMER APELLIDO:</t>
   </si>
   <si>
@@ -69,69 +57,12 @@
     <t xml:space="preserve">DIRECCION DE RESIDENCIA: </t>
   </si>
   <si>
-    <t>DEPARTAMENTO RESIDENCIA:</t>
-  </si>
-  <si>
-    <t>MUNICIPIO RESIDENCIA:</t>
-  </si>
-  <si>
-    <t>ZONA:</t>
-  </si>
-  <si>
-    <t>CARÁCTER:</t>
-  </si>
-  <si>
-    <t>POBLACION VICTIMA DEL CONFLICTO (RUV):</t>
-  </si>
-  <si>
-    <t>CATEGORIA SISBEN IV:</t>
-  </si>
-  <si>
-    <t>SUBCATEGORIA SISBEN IV:</t>
-  </si>
-  <si>
-    <t>ESTRATO:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUENTE DE RECURSOS: </t>
-  </si>
-  <si>
-    <t>RESGUARDO:</t>
-  </si>
-  <si>
-    <t>ETNIA:</t>
-  </si>
-  <si>
     <t>LISTADO DE CATEGORIA DISCAPACIDAD</t>
   </si>
   <si>
-    <t>LISTADO DE TRASTORNOS ESPECIFICOS EN EL APRENDIZAJE ESCOLAR Y EL COMPORTAMIENTO</t>
-  </si>
-  <si>
-    <t>APOYO ACADEMICO ESPECIAL:</t>
-  </si>
-  <si>
-    <t>LISTADO DE CAPACIDADES O TALENTOS EXCEPCIONALES</t>
-  </si>
-  <si>
-    <t>SISTEMA DE RESPONSABILIDAD PENAL PARA ADOLESCENTES (SRPA):</t>
-  </si>
-  <si>
     <t>NO APLICA</t>
   </si>
   <si>
-    <t>NO MATRICULADO</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>CUNDINAMARCA</t>
-  </si>
-  <si>
-    <t>GIRARDOT</t>
-  </si>
-  <si>
     <t>MASCULINO</t>
   </si>
   <si>
@@ -147,29 +78,100 @@
     <t>DAVID</t>
   </si>
   <si>
-    <t>EL DIAMANTE MZ 1 CASA 4</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>GRUPO SANGUINEO:</t>
+  </si>
+  <si>
+    <t>EPS:</t>
+  </si>
+  <si>
+    <t>SISBEN:</t>
+  </si>
+  <si>
+    <t>POBLACION VULNERABLE:</t>
+  </si>
+  <si>
+    <t>TELEFONO:</t>
+  </si>
+  <si>
+    <t>CORREO:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZABON </t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>SANITAS</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>WILLIAMDAVIDGAZABON@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MARCOALBERTOGAZABON@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROSA BLANCA MZ 1 CASA 6</t>
+  </si>
+  <si>
+    <t>GRADO:</t>
+  </si>
+  <si>
+    <t>MATRICULAR:</t>
+  </si>
+  <si>
+    <t>TIPO MATRICULA:</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>DÉCIMO</t>
+  </si>
+  <si>
+    <t>NUEVA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -183,7 +185,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -196,77 +198,51 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -544,251 +520,240 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFE01B7-9CBF-4437-8546-ACAE7377677C}">
+  <dimension ref="A1:T3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.140625" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-    <col min="14" max="14" width="24.85546875" customWidth="1"/>
-    <col min="15" max="15" width="27.140625" customWidth="1"/>
-    <col min="16" max="16" width="22.5703125" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" customWidth="1"/>
-    <col min="19" max="19" width="39.85546875" customWidth="1"/>
-    <col min="20" max="20" width="20.28515625" customWidth="1"/>
-    <col min="21" max="21" width="24.28515625" customWidth="1"/>
-    <col min="22" max="22" width="9.42578125" customWidth="1"/>
-    <col min="23" max="23" width="21.140625" customWidth="1"/>
-    <col min="24" max="24" width="12.28515625" customWidth="1"/>
-    <col min="25" max="25" width="6.85546875" customWidth="1"/>
-    <col min="26" max="26" width="35.42578125" customWidth="1"/>
-    <col min="27" max="27" width="84.7109375" customWidth="1"/>
-    <col min="28" max="28" width="27.85546875" customWidth="1"/>
-    <col min="29" max="29" width="49.7109375" customWidth="1"/>
-    <col min="30" max="30" width="59.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="36.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="4"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="E2" s="5">
+        <v>1071062143</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2">
-        <v>1071062143</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
       </c>
       <c r="G2" s="6">
         <v>38077</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="O2" s="5">
+        <v>3193664511</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L2" t="s">
+      <c r="R2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M2" t="s">
+      <c r="S2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1071143062</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="6">
+        <v>37699</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="P2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2">
-        <v>3</v>
-      </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD2" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="G3" s="6"/>
+      <c r="O3" s="5">
+        <v>3194511366</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z1:Z1048576" xr:uid="{2C74B836-28D5-4F08-891F-A4C296286A13}">
-      <formula1>"DISCAPACIDAD FISICA, DISCAPACIDAD AUDITIVA, VISUAL, SORDOCEGUERA, DISCAPACIDAD INTELECTUAL, DISCAPACIDAD PSICOSOCIAL (MENTAL), DISCAPACIDAD MULTIPLE, NO APLICA"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC1:AC1048576" xr:uid="{932256E0-7F39-45C0-94D4-D7ABF55E219E}">
-      <formula1>"TALENTO EXCEPCIONAL EN TECNOLOGIA, TALENTO EXCEPCIONAL EN LIDERAZGO SOCIAL Y EMPRENDIMIENTO, TALENTO EXCEPCIONAL EN CIENCIAS NATURALES O BASICAS, TALENTO EXCEPCIONAL EN ARTES O EN LETRAS, TALENTO EXCEPCIONAL EN ACTIVIDAD FISICA EJERCICIO Y DEPORTES,NO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{0123EC40-0F0F-4BAE-BD83-E65E52B24F8F}">
-      <formula1>"MATRICULADO, NO MATRICULADO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{BFB05004-D06A-4BD6-B72B-E58E2768F9DF}">
+  <protectedRanges>
+    <protectedRange sqref="A2" name="primerapellido"/>
+  </protectedRanges>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{46D71D1A-F592-4FEE-BAD2-C6D514F3FB86}">
       <formula1>"CC,TI,CE,PT"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{1AFD7E32-16AC-43BD-BD99-9C7EB3D734AE}">
-      <formula1>"MASCULINO,FEMENINO"</formula1>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{06534228-D3C9-4961-8EBF-B0AA374587C7}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{EC575B90-8C54-4911-A225-E59468566A59}">
       <formula1>7306</formula1>
       <formula2>43831</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1" xr:uid="{23EA94A2-A103-4372-9AA6-61EB918E4DE0}">
+      <formula1>"MASCULINO,FEMENINO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Es obligatorio seleccionar" error="selecciona una opcion_x000a_" sqref="M1" xr:uid="{0F64B080-C7EE-4C88-BD54-B6C1DA0EB956}">
+      <formula1>"DISCAPACIDAD FISICA, DISCAPACIDAD AUDITIVA, VISUAL, SORDOCEGUERA, DISCAPACIDAD INTELECTUAL, DISCAPACIDAD PSICOSOCIAL (MENTAL), DISCAPACIDAD MULTIPLE, NO APLICA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576" xr:uid="{8DECCC44-D4F3-49DB-91B4-53D63E86E91D}">
+      <formula1>"DISCAPACIDAD FISICA, DISCAPACIDAD AUDITIVA, VISUAL, SORDOCEGUERA, DISCAPACIDAD INTELECTUAL, DISCAPACIDAD PSICOSOCIAL (MENTAL), DISCAPACIDAD MULTIPLE, NO APLICA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{C7342326-F72E-4F91-8EF3-8CB896B116C8}">
+      <formula1>"CC,TI,CE,PT"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{7CA279A3-AF27-46D9-ADA0-84E5BE1DE788}">
+      <formula1>"SI,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{2030D9DA-99D2-41C6-80CA-C84E19DEA2F6}">
+      <formula1>"NUEVA,RENOVACION,TRASLADO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576" xr:uid="{60A5F218-EB4D-4230-A1F9-F88E62F3B888}">
+      <formula1>"PRIMERO, SEGUNDO, TERCERO, CUARTO, QUINTO, SEXTO, SÉPTIMO, OCTAVO, NOVENO, DÉCIMO, UNDÉCIMO"</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="P2" r:id="rId1" xr:uid="{A856EE98-C210-4058-8552-B7C249DB2EFF}"/>
+    <hyperlink ref="P3" r:id="rId2" xr:uid="{E2ECB0B9-CFC9-4973-B57C-50C33743B0C3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>